--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>0.5160979999999999</v>
+        <v>0.07296800000000001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>0.07296800000000001</v>
+        <v>-0.039594</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.039594</v>
+        <v>-1.263156</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-1.263156</v>
+        <v>0.1319</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>0.1319</v>
+        <v>-0.053015</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.053015</v>
+        <v>-0.143535</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.143535</v>
+        <v>-0.612188</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.612188</v>
+        <v>-1.305565</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-1.305565</v>
+        <v>-0.9013099999999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.9013099999999999</v>
+        <v>0.140417</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>0.140417</v>
+        <v>0.200172</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>0.200172</v>
+        <v>0.57506</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>0.57506</v>
+        <v>2.404988</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>2.404988</v>
+        <v>3.340086</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>3.340086</v>
+        <v>3.333473</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>3.333473</v>
+        <v>2.268081</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>2.268081</v>
+        <v>1.647176</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>1.647176</v>
+        <v>1.607537</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>1.607537</v>
+        <v>2.255024</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>2.255024</v>
+        <v>2.646214</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>2.646214</v>
+        <v>2.019042</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>2.019042</v>
+        <v>2.004518</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>2.004518</v>
+        <v>1.529193</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>1.529193</v>
+        <v>1.548375</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>1.548375</v>
+        <v>2.677676</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>2.677676</v>
+        <v>2.623735</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -434,482 +434,482 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="B2" t="n">
-        <v>7.265832</v>
+        <v>0.25358</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="B3" t="n">
-        <v>0.25358</v>
+        <v>0.690446</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>44592</v>
       </c>
       <c r="B4" t="n">
-        <v>0.690446</v>
+        <v>-8.981097</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44592</v>
+        <v>44620</v>
       </c>
       <c r="B5" t="n">
-        <v>-8.981097</v>
+        <v>-3.430362</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44620</v>
+        <v>44651</v>
       </c>
       <c r="B6" t="n">
-        <v>-3.430362</v>
+        <v>3.411428</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44651</v>
+        <v>44681</v>
       </c>
       <c r="B7" t="n">
-        <v>3.411428</v>
+        <v>-13.261681</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44681</v>
+        <v>44712</v>
       </c>
       <c r="B8" t="n">
-        <v>-13.261681</v>
+        <v>-2.053161</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="B9" t="n">
-        <v>-2.053161</v>
+        <v>-8.712982999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44742</v>
+        <v>44773</v>
       </c>
       <c r="B10" t="n">
-        <v>-8.712982999999999</v>
+        <v>12.3491</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="B11" t="n">
-        <v>12.3491</v>
+        <v>-4.636467</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B12" t="n">
-        <v>-4.636467</v>
+        <v>-10.498976</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B13" t="n">
-        <v>-10.498976</v>
+        <v>3.900767</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B14" t="n">
-        <v>3.900767</v>
+        <v>4.366973</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44895</v>
+        <v>44926</v>
       </c>
       <c r="B15" t="n">
-        <v>4.366973</v>
+        <v>-8.733166000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44926</v>
+        <v>44957</v>
       </c>
       <c r="B16" t="n">
-        <v>-8.733166000000001</v>
+        <v>10.682381</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44957</v>
+        <v>44985</v>
       </c>
       <c r="B17" t="n">
-        <v>10.682381</v>
+        <v>-1.113636</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>44985</v>
+        <v>45016</v>
       </c>
       <c r="B18" t="n">
-        <v>-1.113636</v>
+        <v>6.689952</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45016</v>
+        <v>45046</v>
       </c>
       <c r="B19" t="n">
-        <v>6.689952</v>
+        <v>0.038209</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45046</v>
+        <v>45077</v>
       </c>
       <c r="B20" t="n">
-        <v>0.038209</v>
+        <v>5.796469</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B21" t="n">
-        <v>5.796469</v>
+        <v>6.591502</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B22" t="n">
-        <v>6.591502</v>
+        <v>4.047743</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B23" t="n">
-        <v>4.047743</v>
+        <v>-2.168196</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45169</v>
+        <v>45199</v>
       </c>
       <c r="B24" t="n">
-        <v>-2.168196</v>
+        <v>-5.811551</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="B25" t="n">
-        <v>-5.811551</v>
+        <v>-2.78441</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B26" t="n">
-        <v>-2.78441</v>
+        <v>10.699197</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45260</v>
+        <v>45291</v>
       </c>
       <c r="B27" t="n">
-        <v>10.699197</v>
+        <v>5.518893</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45291</v>
+        <v>45322</v>
       </c>
       <c r="B28" t="n">
-        <v>5.518893</v>
+        <v>1.016965</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B29" t="n">
-        <v>1.016965</v>
+        <v>6.119161</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45351</v>
+        <v>45382</v>
       </c>
       <c r="B30" t="n">
-        <v>6.119161</v>
+        <v>1.78686</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45382</v>
+        <v>45412</v>
       </c>
       <c r="B31" t="n">
-        <v>1.78686</v>
+        <v>-4.40576</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B32" t="n">
-        <v>-4.40576</v>
+        <v>6.879624</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B33" t="n">
-        <v>6.879624</v>
+        <v>5.961033</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45473</v>
+        <v>45504</v>
       </c>
       <c r="B34" t="n">
-        <v>5.961033</v>
+        <v>-0.751154</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45504</v>
+        <v>45535</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.751154</v>
+        <v>0.648992</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45535</v>
+        <v>45565</v>
       </c>
       <c r="B36" t="n">
-        <v>0.648992</v>
+        <v>2.684662</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B37" t="n">
-        <v>2.684662</v>
+        <v>-0.516898</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45596</v>
+        <v>45626</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.516898</v>
+        <v>6.206191</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45626</v>
+        <v>45657</v>
       </c>
       <c r="B39" t="n">
-        <v>6.206191</v>
+        <v>0.481935</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45657</v>
+        <v>45688</v>
       </c>
       <c r="B40" t="n">
-        <v>0.481935</v>
+        <v>1.639759</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45688</v>
+        <v>45716</v>
       </c>
       <c r="B41" t="n">
-        <v>1.639759</v>
+        <v>-3.974844</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45716</v>
+        <v>45747</v>
       </c>
       <c r="B42" t="n">
-        <v>-3.974844</v>
+        <v>-8.213335000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B43" t="n">
-        <v>-8.213335000000001</v>
+        <v>0.850039</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45777</v>
+        <v>45808</v>
       </c>
       <c r="B44" t="n">
-        <v>0.850039</v>
+        <v>9.557475999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45808</v>
+        <v>45838</v>
       </c>
       <c r="B45" t="n">
-        <v>9.557475999999999</v>
+        <v>6.570975</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B46" t="n">
-        <v>6.570975</v>
+        <v>3.695281</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45869</v>
+        <v>45900</v>
       </c>
       <c r="B47" t="n">
-        <v>3.695281</v>
+        <v>1.577003</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45900</v>
+        <v>45930</v>
       </c>
       <c r="B48" t="n">
-        <v>1.577003</v>
+        <v>5.613741</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B49" t="n">
-        <v>5.613741</v>
+        <v>4.699694</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45961</v>
+        <v>45991</v>
       </c>
       <c r="B50" t="n">
-        <v>4.699694</v>
+        <v>-1.514319</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="B51" t="n">
-        <v>-1.514319</v>
+        <v>-0.529405</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.529405</v>
+        <v>0.945832</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B53" t="n">
-        <v>0.945832</v>
+        <v>-3.382557</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="B54" t="n">
-        <v>-3.382557</v>
+        <v>-4.753706</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B55" t="n">
-        <v>-4.753706</v>
+        <v>15.292187</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="B56" t="n">
-        <v>15.292187</v>
+        <v>8.357234</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="B57" t="n">
-        <v>8.357234</v>
+        <v>-2.813588</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="B58" t="n">
-        <v>-2.813588</v>
+        <v>-3.203937</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="B59" t="n">
-        <v>-3.203937</v>
+        <v>3.929404</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="B60" t="n">
-        <v>3.929404</v>
+        <v>1.858754</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>2.623735</v>
+        <v>-0.158047</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.158047</v>
+        <v>1.302362</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>1.302362</v>
+        <v>1.3442</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>1.3442</v>
+        <v>1.227795</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>1.227795</v>
+        <v>2.397217</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>2.397217</v>
+        <v>2.985386</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>2.985386</v>
+        <v>2.371281</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>2.371281</v>
+        <v>1.161482</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>1.161482</v>
+        <v>1.35558</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>1.35558</v>
+        <v>1.820595</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>1.820595</v>
+        <v>1.917448</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>1.917448</v>
+        <v>1.880452</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>1.880452</v>
+        <v>1.403344</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>1.403344</v>
+        <v>1.466</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>1.466</v>
+        <v>1.215209</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>1.215209</v>
+        <v>0.348364</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>0.348364</v>
+        <v>0.300068</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>0.300068</v>
+        <v>-1.519364</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-1.519364</v>
+        <v>-1.345727</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-1.345727</v>
+        <v>-2.684299</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-2.684299</v>
+        <v>-1.260407</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-1.260407</v>
+        <v>-1.177493</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-1.177493</v>
+        <v>-0.94504</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.94504</v>
+        <v>-2.845691</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-2.845691</v>
+        <v>-3.306541</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-3.306541</v>
+        <v>-3.371872</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-3.371872</v>
+        <v>-2.401238</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-2.401238</v>
+        <v>-1.53736</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -909,7 +909,7 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>-1.53736</v>
+        <v>-1.519116</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,482 +434,474 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>0.25358</v>
+        <v>0.690446</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44561</v>
+        <v>44592</v>
       </c>
       <c r="B3" t="n">
-        <v>0.690446</v>
+        <v>-8.981097</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44592</v>
+        <v>44620</v>
       </c>
       <c r="B4" t="n">
-        <v>-8.981097</v>
+        <v>-3.430362</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44620</v>
+        <v>44651</v>
       </c>
       <c r="B5" t="n">
-        <v>-3.430362</v>
+        <v>3.411428</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44651</v>
+        <v>44681</v>
       </c>
       <c r="B6" t="n">
-        <v>3.411428</v>
+        <v>-13.261681</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44681</v>
+        <v>44712</v>
       </c>
       <c r="B7" t="n">
-        <v>-13.261681</v>
+        <v>-2.053161</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="B8" t="n">
-        <v>-2.053161</v>
+        <v>-8.712982999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44742</v>
+        <v>44773</v>
       </c>
       <c r="B9" t="n">
-        <v>-8.712982999999999</v>
+        <v>12.3491</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="B10" t="n">
-        <v>12.3491</v>
+        <v>-4.636467</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B11" t="n">
-        <v>-4.636467</v>
+        <v>-10.498976</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B12" t="n">
-        <v>-10.498976</v>
+        <v>3.900767</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B13" t="n">
-        <v>3.900767</v>
+        <v>4.366973</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44895</v>
+        <v>44926</v>
       </c>
       <c r="B14" t="n">
-        <v>4.366973</v>
+        <v>-8.733166000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44926</v>
+        <v>44957</v>
       </c>
       <c r="B15" t="n">
-        <v>-8.733166000000001</v>
+        <v>10.682381</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44957</v>
+        <v>44985</v>
       </c>
       <c r="B16" t="n">
-        <v>10.682381</v>
+        <v>-1.113636</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44985</v>
+        <v>45016</v>
       </c>
       <c r="B17" t="n">
-        <v>-1.113636</v>
+        <v>6.689952</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45016</v>
+        <v>45046</v>
       </c>
       <c r="B18" t="n">
-        <v>6.689952</v>
+        <v>0.038209</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45046</v>
+        <v>45077</v>
       </c>
       <c r="B19" t="n">
-        <v>0.038209</v>
+        <v>5.796469</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B20" t="n">
-        <v>5.796469</v>
+        <v>6.591502</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B21" t="n">
-        <v>6.591502</v>
+        <v>4.047743</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B22" t="n">
-        <v>4.047743</v>
+        <v>-2.168196</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45169</v>
+        <v>45199</v>
       </c>
       <c r="B23" t="n">
-        <v>-2.168196</v>
+        <v>-5.811551</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="B24" t="n">
-        <v>-5.811551</v>
+        <v>-2.78441</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B25" t="n">
-        <v>-2.78441</v>
+        <v>10.699197</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45260</v>
+        <v>45291</v>
       </c>
       <c r="B26" t="n">
-        <v>10.699197</v>
+        <v>5.518893</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45291</v>
+        <v>45322</v>
       </c>
       <c r="B27" t="n">
-        <v>5.518893</v>
+        <v>1.016965</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B28" t="n">
-        <v>1.016965</v>
+        <v>6.119161</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45351</v>
+        <v>45382</v>
       </c>
       <c r="B29" t="n">
-        <v>6.119161</v>
+        <v>1.78686</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45382</v>
+        <v>45412</v>
       </c>
       <c r="B30" t="n">
-        <v>1.78686</v>
+        <v>-4.40576</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B31" t="n">
-        <v>-4.40576</v>
+        <v>6.879624</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B32" t="n">
-        <v>6.879624</v>
+        <v>5.961033</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45473</v>
+        <v>45504</v>
       </c>
       <c r="B33" t="n">
-        <v>5.961033</v>
+        <v>-0.751154</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45504</v>
+        <v>45535</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.751154</v>
+        <v>0.648992</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45535</v>
+        <v>45565</v>
       </c>
       <c r="B35" t="n">
-        <v>0.648992</v>
+        <v>2.684662</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B36" t="n">
-        <v>2.684662</v>
+        <v>-0.516898</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45596</v>
+        <v>45626</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.516898</v>
+        <v>6.206191</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45626</v>
+        <v>45657</v>
       </c>
       <c r="B38" t="n">
-        <v>6.206191</v>
+        <v>0.481935</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45657</v>
+        <v>45688</v>
       </c>
       <c r="B39" t="n">
-        <v>0.481935</v>
+        <v>1.639759</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45688</v>
+        <v>45716</v>
       </c>
       <c r="B40" t="n">
-        <v>1.639759</v>
+        <v>-3.974844</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45716</v>
+        <v>45747</v>
       </c>
       <c r="B41" t="n">
-        <v>-3.974844</v>
+        <v>-8.213335000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B42" t="n">
-        <v>-8.213335000000001</v>
+        <v>0.850039</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45777</v>
+        <v>45808</v>
       </c>
       <c r="B43" t="n">
-        <v>0.850039</v>
+        <v>9.557475999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45808</v>
+        <v>45838</v>
       </c>
       <c r="B44" t="n">
-        <v>9.557475999999999</v>
+        <v>6.570975</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B45" t="n">
-        <v>6.570975</v>
+        <v>3.695281</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45869</v>
+        <v>45900</v>
       </c>
       <c r="B46" t="n">
-        <v>3.695281</v>
+        <v>1.577003</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45900</v>
+        <v>45930</v>
       </c>
       <c r="B47" t="n">
-        <v>1.577003</v>
+        <v>5.613741</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B48" t="n">
-        <v>5.613741</v>
+        <v>4.699694</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45961</v>
+        <v>45991</v>
       </c>
       <c r="B49" t="n">
-        <v>4.699694</v>
+        <v>-1.514319</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="B50" t="n">
-        <v>-1.514319</v>
+        <v>-0.529405</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.529405</v>
+        <v>0.945832</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B52" t="n">
-        <v>0.945832</v>
+        <v>-3.382557</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="B53" t="n">
-        <v>-3.382557</v>
+        <v>-4.753706</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B54" t="n">
-        <v>-4.753706</v>
+        <v>15.292187</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="B55" t="n">
-        <v>15.292187</v>
+        <v>8.357234</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="B56" t="n">
-        <v>8.357234</v>
+        <v>-2.813588</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="B57" t="n">
-        <v>-2.813588</v>
+        <v>-3.203937</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="B58" t="n">
-        <v>-3.203937</v>
+        <v>3.929404</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="B59" t="n">
-        <v>3.929404</v>
+        <v>1.858754</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="B60" t="n">
-        <v>1.858754</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="n">
-        <v>46326</v>
-      </c>
-      <c r="B61" t="n">
-        <v>-1.519116</v>
+        <v>-5.142995</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/yahoo_ret_nasdaq.xlsx
+++ b/data/final/series/yahoo_ret_nasdaq.xlsx
@@ -901,7 +901,7 @@
         <v>46326</v>
       </c>
       <c r="B60" t="n">
-        <v>-5.142995</v>
+        <v>-5.30158</v>
       </c>
     </row>
   </sheetData>
